--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,2059 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129281686</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105732</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516457</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6364782</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129281693</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100875</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516390</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6365027</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129281682</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516475</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6364922</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129281692</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109316</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516380</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6365010</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129281691</v>
+      </c>
+      <c r="B8" t="n">
+        <v>109528</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516350</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6364947</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129281694</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100875</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516400</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6365033</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129281684</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107376</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516455</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6364653</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129281696</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100875</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516417</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6364985</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129281683</v>
+      </c>
+      <c r="B12" t="n">
+        <v>109528</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516465</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6364622</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129281689</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98706</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516373</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365017</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129281673</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91305</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516468</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6364843</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129281678</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516445</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6364775</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129281680</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516471</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6364826</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129281687</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105732</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516474</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6364865</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129281670</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96158</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516468</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6364905</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129281679</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516463</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6364811</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129281677</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516446</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6364783</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129281676</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516432</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6364723</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129281675</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516460</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6364645</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129281672</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91305</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>516460</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6364925</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129281681</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>S Venen, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>516465</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6364843</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,49 +1023,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>100875</v>
+        <v>92833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R5" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,45 +1120,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>100882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R6" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>109316</v>
+        <v>109535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109528</v>
+        <v>109323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
         <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>100875</v>
+        <v>100882</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107376</v>
+        <v>107383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,49 +1613,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>100875</v>
+        <v>109535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R11" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,52 +1703,56 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>109528</v>
+        <v>100882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R12" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>92833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R13" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>129281673</v>
       </c>
       <c r="B14" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>92826</v>
+        <v>98713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281680</v>
+        <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>92826</v>
+        <v>96165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516471</v>
+        <v>516468</v>
       </c>
       <c r="R16" t="n">
-        <v>6364826</v>
+        <v>6364905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281687</v>
+        <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>105732</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,38 +2210,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516474</v>
+        <v>516471</v>
       </c>
       <c r="R17" t="n">
-        <v>6364865</v>
+        <v>6364826</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281670</v>
+        <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>96158</v>
+        <v>105739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,34 +2307,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516468</v>
+        <v>516474</v>
       </c>
       <c r="R18" t="n">
-        <v>6364905</v>
+        <v>6364865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>100882</v>
+        <v>100884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B7" t="n">
-        <v>109535</v>
+        <v>109325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R7" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109323</v>
+        <v>109537</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R8" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
         <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>100882</v>
+        <v>100884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107383</v>
+        <v>107385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109535</v>
+        <v>109537</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100882</v>
+        <v>100884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129281678</v>
       </c>
       <c r="B13" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>129281673</v>
       </c>
       <c r="B14" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>98713</v>
+        <v>98715</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281670</v>
+        <v>129281687</v>
       </c>
       <c r="B16" t="n">
-        <v>96165</v>
+        <v>105741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,34 +2113,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516468</v>
+        <v>516474</v>
       </c>
       <c r="R16" t="n">
-        <v>6364905</v>
+        <v>6364865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,10 +2203,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281680</v>
+        <v>129281670</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>96167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,21 +2214,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2234,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516471</v>
+        <v>516468</v>
       </c>
       <c r="R17" t="n">
-        <v>6364826</v>
+        <v>6364905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281687</v>
+        <v>129281680</v>
       </c>
       <c r="B18" t="n">
-        <v>105739</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,38 +2311,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516474</v>
+        <v>516471</v>
       </c>
       <c r="R18" t="n">
-        <v>6364865</v>
+        <v>6364826</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Jana Hedlund, Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>91314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R13" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281673</v>
+        <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>91314</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516468</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6364843</v>
+        <v>6364775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281687</v>
+        <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>105741</v>
+        <v>96167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,38 +2113,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516474</v>
+        <v>516468</v>
       </c>
       <c r="R16" t="n">
-        <v>6364865</v>
+        <v>6364905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281670</v>
+        <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>96167</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2214,21 +2210,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516468</v>
+        <v>516471</v>
       </c>
       <c r="R17" t="n">
-        <v>6364905</v>
+        <v>6364826</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>105741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,34 +2307,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R18" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1023,45 +1023,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>100884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R5" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,49 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B6" t="n">
-        <v>100884</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R6" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,45 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281692</v>
+        <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>109325</v>
+        <v>100884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220228</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516380</v>
+        <v>516400</v>
       </c>
       <c r="R7" t="n">
-        <v>6365010</v>
+        <v>6365033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109537</v>
+        <v>109325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,49 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B9" t="n">
-        <v>100884</v>
+        <v>109537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R9" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129281693</v>
       </c>
       <c r="B5" t="n">
-        <v>100884</v>
+        <v>100910</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129281682</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,49 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>100884</v>
+        <v>109563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1321,7 @@
         <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109325</v>
+        <v>109351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,45 +1415,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>109537</v>
+        <v>100910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R9" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107385</v>
+        <v>107411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109537</v>
+        <v>109563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100884</v>
+        <v>100910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jana Hedlund, Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
         <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>98715</v>
+        <v>98741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,49 +1023,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>100910</v>
+        <v>92822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R5" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,45 +1120,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>100912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R6" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>109563</v>
+        <v>109565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109351</v>
+        <v>109353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>100910</v>
+        <v>100912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107411</v>
+        <v>107413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109563</v>
+        <v>109565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100910</v>
+        <v>100912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B14" t="n">
-        <v>92821</v>
+        <v>98742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R14" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B15" t="n">
-        <v>98741</v>
+        <v>92822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R15" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92859</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92821</v>
+        <v>92860</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>100912</v>
+        <v>100913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>109565</v>
+        <v>109566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109353</v>
+        <v>109354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>100912</v>
+        <v>100913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107413</v>
+        <v>107414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109565</v>
+        <v>109566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100912</v>
+        <v>100913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B13" t="n">
-        <v>91313</v>
+        <v>98743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R13" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>98742</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B15" t="n">
-        <v>92822</v>
+        <v>91313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R15" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>100913</v>
+        <v>100917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,45 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>109566</v>
+        <v>100917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R7" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109354</v>
+        <v>109570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R8" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,49 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281694</v>
+        <v>129281692</v>
       </c>
       <c r="B9" t="n">
-        <v>100913</v>
+        <v>109358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222886</v>
+        <v>220228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516400</v>
+        <v>516380</v>
       </c>
       <c r="R9" t="n">
-        <v>6365033</v>
+        <v>6365010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107414</v>
+        <v>107418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,45 +1613,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B11" t="n">
-        <v>109566</v>
+        <v>100917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R11" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,56 +1707,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B12" t="n">
-        <v>100913</v>
+        <v>109570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R12" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281689</v>
+        <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>98743</v>
+        <v>91316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219875</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516373</v>
+        <v>516468</v>
       </c>
       <c r="R13" t="n">
-        <v>6365017</v>
+        <v>6364843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>91313</v>
+        <v>98747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>105774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,34 +2210,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R17" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281687</v>
+        <v>129281680</v>
       </c>
       <c r="B18" t="n">
-        <v>105770</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,38 +2311,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516474</v>
+        <v>516471</v>
       </c>
       <c r="R18" t="n">
-        <v>6364865</v>
+        <v>6364826</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1221,49 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>100917</v>
+        <v>109570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109570</v>
+        <v>109358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,45 +1415,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281692</v>
+        <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>109358</v>
+        <v>100917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220228</v>
+        <v>222886</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516380</v>
+        <v>516400</v>
       </c>
       <c r="R9" t="n">
-        <v>6365010</v>
+        <v>6365033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281687</v>
+        <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>105774</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,38 +2210,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516474</v>
+        <v>516471</v>
       </c>
       <c r="R17" t="n">
-        <v>6364865</v>
+        <v>6364826</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>105774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,34 +2307,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R18" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92825</v>
+        <v>92863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,45 +1023,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>100919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R5" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,49 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B6" t="n">
-        <v>100917</v>
+        <v>92827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R6" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>109570</v>
+        <v>109572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109358</v>
+        <v>109360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>100917</v>
+        <v>100919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107418</v>
+        <v>107420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,49 +1613,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>100917</v>
+        <v>109572</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R11" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,52 +1703,56 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>109570</v>
+        <v>100919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R12" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281673</v>
+        <v>129281678</v>
       </c>
       <c r="B13" t="n">
-        <v>91316</v>
+        <v>92827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516468</v>
+        <v>516445</v>
       </c>
       <c r="R13" t="n">
-        <v>6364843</v>
+        <v>6364775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B14" t="n">
-        <v>92825</v>
+        <v>98749</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R14" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281689</v>
+        <v>129281673</v>
       </c>
       <c r="B15" t="n">
-        <v>98747</v>
+        <v>91318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516373</v>
+        <v>516468</v>
       </c>
       <c r="R15" t="n">
-        <v>6365017</v>
+        <v>6364843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281670</v>
+        <v>129281687</v>
       </c>
       <c r="B16" t="n">
-        <v>96199</v>
+        <v>105776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,34 +2113,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516468</v>
+        <v>516474</v>
       </c>
       <c r="R16" t="n">
-        <v>6364905</v>
+        <v>6364865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2206,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281687</v>
+        <v>129281670</v>
       </c>
       <c r="B18" t="n">
-        <v>105774</v>
+        <v>96201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,38 +2311,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516474</v>
+        <v>516468</v>
       </c>
       <c r="R18" t="n">
-        <v>6364865</v>
+        <v>6364905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92863</v>
+        <v>92827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92825</v>
+        <v>92865</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129281693</v>
       </c>
       <c r="B5" t="n">
-        <v>100919</v>
+        <v>100923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>129281682</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,45 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>109572</v>
+        <v>100923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R7" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109360</v>
+        <v>109576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R8" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,49 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281694</v>
+        <v>129281692</v>
       </c>
       <c r="B9" t="n">
-        <v>100919</v>
+        <v>109364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222886</v>
+        <v>220228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516400</v>
+        <v>516380</v>
       </c>
       <c r="R9" t="n">
-        <v>6365033</v>
+        <v>6365010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107420</v>
+        <v>107424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109572</v>
+        <v>109576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100919</v>
+        <v>100923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>92827</v>
+        <v>91322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R13" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>98749</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>91318</v>
+        <v>98753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281687</v>
+        <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>105776</v>
+        <v>96205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,38 +2113,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516474</v>
+        <v>516468</v>
       </c>
       <c r="R16" t="n">
-        <v>6364865</v>
+        <v>6364905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2202,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281670</v>
+        <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>96201</v>
+        <v>105780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,34 +2307,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516468</v>
+        <v>516474</v>
       </c>
       <c r="R18" t="n">
-        <v>6364905</v>
+        <v>6364865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92865</v>
+        <v>92831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,49 +1023,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>100923</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R5" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,45 +1120,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>100931</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R6" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,49 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>100923</v>
+        <v>109586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109576</v>
+        <v>109374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,45 +1415,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281692</v>
+        <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>109364</v>
+        <v>100931</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220228</v>
+        <v>222886</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516380</v>
+        <v>516400</v>
       </c>
       <c r="R9" t="n">
-        <v>6365010</v>
+        <v>6365033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107424</v>
+        <v>107434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,45 +1613,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B11" t="n">
-        <v>109576</v>
+        <v>100931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R11" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,56 +1707,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B12" t="n">
-        <v>100923</v>
+        <v>109586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R12" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B13" t="n">
-        <v>91322</v>
+        <v>98761</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R13" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>91323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R14" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B15" t="n">
-        <v>98753</v>
+        <v>92832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R15" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>105790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,34 +2210,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R17" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281687</v>
+        <v>129281680</v>
       </c>
       <c r="B18" t="n">
-        <v>105780</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,38 +2311,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516474</v>
+        <v>516471</v>
       </c>
       <c r="R18" t="n">
-        <v>6364865</v>
+        <v>6364826</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92831</v>
+        <v>92870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1613,49 +1613,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>100931</v>
+        <v>109586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R11" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,52 +1703,56 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>109586</v>
+        <v>100931</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R12" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B13" t="n">
-        <v>98761</v>
+        <v>92832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R13" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>98761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281670</v>
+        <v>129281680</v>
       </c>
       <c r="B16" t="n">
-        <v>96213</v>
+        <v>92832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516468</v>
+        <v>516471</v>
       </c>
       <c r="R16" t="n">
-        <v>6364905</v>
+        <v>6364826</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281687</v>
+        <v>129281670</v>
       </c>
       <c r="B17" t="n">
-        <v>105790</v>
+        <v>96213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,38 +2210,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516474</v>
+        <v>516468</v>
       </c>
       <c r="R17" t="n">
-        <v>6364865</v>
+        <v>6364905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>105790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,34 +2307,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R18" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>92870</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92870</v>
+        <v>92832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1023,45 +1023,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>100931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R5" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,49 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B6" t="n">
-        <v>100931</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R6" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,45 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>109586</v>
+        <v>100931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R7" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109374</v>
+        <v>109586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R8" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,49 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281694</v>
+        <v>129281692</v>
       </c>
       <c r="B9" t="n">
-        <v>100931</v>
+        <v>109374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222886</v>
+        <v>220228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516400</v>
+        <v>516380</v>
       </c>
       <c r="R9" t="n">
-        <v>6365033</v>
+        <v>6365010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>92832</v>
+        <v>91323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R13" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B14" t="n">
-        <v>91323</v>
+        <v>98761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R14" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B15" t="n">
-        <v>98761</v>
+        <v>92832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R15" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281680</v>
+        <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>92832</v>
+        <v>96213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516471</v>
+        <v>516468</v>
       </c>
       <c r="R16" t="n">
-        <v>6364826</v>
+        <v>6364905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281670</v>
+        <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>96213</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,21 +2210,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516468</v>
+        <v>516471</v>
       </c>
       <c r="R17" t="n">
-        <v>6364905</v>
+        <v>6364826</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,49 +1023,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>100931</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R5" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,45 +1120,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>100934</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R6" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,49 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>100931</v>
+        <v>109589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109586</v>
+        <v>109377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,45 +1415,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281692</v>
+        <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>109374</v>
+        <v>100934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220228</v>
+        <v>222886</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516380</v>
+        <v>516400</v>
       </c>
       <c r="R9" t="n">
-        <v>6365010</v>
+        <v>6365033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107434</v>
+        <v>107437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109586</v>
+        <v>109589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100931</v>
+        <v>100934</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>98761</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>98764</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92870</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92832</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1221,45 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>109589</v>
+        <v>100934</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R7" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,49 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B9" t="n">
-        <v>100934</v>
+        <v>109589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R9" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281673</v>
+        <v>129281678</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516468</v>
+        <v>516445</v>
       </c>
       <c r="R13" t="n">
-        <v>6364843</v>
+        <v>6364775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R14" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109377</v>
+        <v>109589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R8" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B9" t="n">
-        <v>109589</v>
+        <v>109377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R9" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>98764</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R14" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281689</v>
+        <v>129281673</v>
       </c>
       <c r="B15" t="n">
-        <v>98764</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516373</v>
+        <v>516468</v>
       </c>
       <c r="R15" t="n">
-        <v>6365017</v>
+        <v>6364843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1221,49 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>100934</v>
+        <v>109589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,45 +1318,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B8" t="n">
-        <v>109589</v>
+        <v>100934</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1613,45 +1613,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B11" t="n">
-        <v>109589</v>
+        <v>100934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R11" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,56 +1707,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jana Hedlund, Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B12" t="n">
-        <v>100934</v>
+        <v>109589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R12" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,17 +1804,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R13" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>98764</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281673</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>98764</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516468</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364843</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281670</v>
+        <v>129281680</v>
       </c>
       <c r="B16" t="n">
-        <v>96216</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516468</v>
+        <v>516471</v>
       </c>
       <c r="R16" t="n">
-        <v>6364905</v>
+        <v>6364826</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281680</v>
+        <v>129281670</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>96216</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,21 +2210,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516471</v>
+        <v>516468</v>
       </c>
       <c r="R17" t="n">
-        <v>6364826</v>
+        <v>6364905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1318,49 +1318,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281694</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>100934</v>
+        <v>109377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222886</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516400</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6365033</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,45 +1415,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281692</v>
+        <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>109377</v>
+        <v>100934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220228</v>
+        <v>222886</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516380</v>
+        <v>516400</v>
       </c>
       <c r="R9" t="n">
-        <v>6365010</v>
+        <v>6365033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1613,49 +1613,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>100934</v>
+        <v>109589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R11" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,52 +1703,56 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jana Hedlund, Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>109589</v>
+        <v>100934</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R12" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>98764</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R14" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281689</v>
+        <v>129281678</v>
       </c>
       <c r="B15" t="n">
-        <v>98764</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219875</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516373</v>
+        <v>516445</v>
       </c>
       <c r="R15" t="n">
-        <v>6365017</v>
+        <v>6364775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281673</v>
+        <v>129281678</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516468</v>
+        <v>516445</v>
       </c>
       <c r="R13" t="n">
-        <v>6364843</v>
+        <v>6364775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281689</v>
+        <v>129281673</v>
       </c>
       <c r="B14" t="n">
-        <v>98764</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219875</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516373</v>
+        <v>516468</v>
       </c>
       <c r="R14" t="n">
-        <v>6365017</v>
+        <v>6364843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129281678</v>
+        <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>98764</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>219875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516445</v>
+        <v>516373</v>
       </c>
       <c r="R15" t="n">
-        <v>6364775</v>
+        <v>6365017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>105793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,34 +2113,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R16" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,10 +2203,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281670</v>
+        <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>96216</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,21 +2214,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2234,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516468</v>
+        <v>516471</v>
       </c>
       <c r="R17" t="n">
-        <v>6364905</v>
+        <v>6364826</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281687</v>
+        <v>129281670</v>
       </c>
       <c r="B18" t="n">
-        <v>105793</v>
+        <v>96216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,38 +2311,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516474</v>
+        <v>516468</v>
       </c>
       <c r="R18" t="n">
-        <v>6364865</v>
+        <v>6364905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>100934</v>
+        <v>100963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>109589</v>
+        <v>109618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109377</v>
+        <v>109406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>100934</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107437</v>
+        <v>107466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281683</v>
       </c>
       <c r="B11" t="n">
-        <v>109589</v>
+        <v>109618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>129281696</v>
       </c>
       <c r="B12" t="n">
-        <v>100934</v>
+        <v>100963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129281678</v>
+        <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>91354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516445</v>
+        <v>516468</v>
       </c>
       <c r="R13" t="n">
-        <v>6364775</v>
+        <v>6364843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129281673</v>
+        <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>92863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516468</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6364843</v>
+        <v>6364775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +2008,7 @@
         <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>98764</v>
+        <v>98793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129281687</v>
+        <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>105793</v>
+        <v>96245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,38 +2113,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516474</v>
+        <v>516468</v>
       </c>
       <c r="R16" t="n">
-        <v>6364865</v>
+        <v>6364905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>105822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2214,34 +2210,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R17" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281670</v>
+        <v>129281680</v>
       </c>
       <c r="B18" t="n">
-        <v>96216</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516468</v>
+        <v>516471</v>
       </c>
       <c r="R18" t="n">
-        <v>6364905</v>
+        <v>6364826</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92873</v>
+        <v>92863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -1023,45 +1023,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R5" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,49 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R6" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,45 +1221,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281691</v>
+        <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>109618</v>
+        <v>100963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516350</v>
+        <v>516400</v>
       </c>
       <c r="R7" t="n">
-        <v>6364947</v>
+        <v>6365033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281692</v>
+        <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109406</v>
+        <v>109618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1353,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516380</v>
+        <v>516350</v>
       </c>
       <c r="R8" t="n">
-        <v>6365010</v>
+        <v>6364947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,49 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281694</v>
+        <v>129281692</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>109406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222886</v>
+        <v>220228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516400</v>
+        <v>516380</v>
       </c>
       <c r="R9" t="n">
-        <v>6365033</v>
+        <v>6365010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129281687</v>
+        <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>105822</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,38 +2210,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516474</v>
+        <v>516471</v>
       </c>
       <c r="R17" t="n">
-        <v>6364865</v>
+        <v>6364826</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129281680</v>
+        <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>105822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,34 +2307,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516471</v>
+        <v>516474</v>
       </c>
       <c r="R18" t="n">
-        <v>6364826</v>
+        <v>6364865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,49 +1023,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281693</v>
+        <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222886</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516390</v>
+        <v>516475</v>
       </c>
       <c r="R5" t="n">
-        <v>6365027</v>
+        <v>6364922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,45 +1120,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281682</v>
+        <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>100975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>222886</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516475</v>
+        <v>516390</v>
       </c>
       <c r="R6" t="n">
-        <v>6364922</v>
+        <v>6365027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>129281694</v>
       </c>
       <c r="B7" t="n">
-        <v>100963</v>
+        <v>100975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129281691</v>
       </c>
       <c r="B8" t="n">
-        <v>109618</v>
+        <v>109630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>129281692</v>
       </c>
       <c r="B9" t="n">
-        <v>109406</v>
+        <v>109418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107466</v>
+        <v>107478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,45 +1613,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281683</v>
+        <v>129281696</v>
       </c>
       <c r="B11" t="n">
-        <v>109618</v>
+        <v>100975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>222886</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516465</v>
+        <v>516417</v>
       </c>
       <c r="R11" t="n">
-        <v>6364622</v>
+        <v>6364985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,56 +1707,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281696</v>
+        <v>129281683</v>
       </c>
       <c r="B12" t="n">
-        <v>100963</v>
+        <v>109630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516417</v>
+        <v>516465</v>
       </c>
       <c r="R12" t="n">
-        <v>6364985</v>
+        <v>6364622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Jana Hedlund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
         <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>98793</v>
+        <v>98805</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B20" t="n">
-        <v>92863</v>
+        <v>92907</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R20" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B21" t="n">
-        <v>92901</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R21" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 47339-2025 artfynd.xlsx
+++ b/artfynd/A 47339-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129281686</v>
       </c>
       <c r="B4" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>129281682</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>129281693</v>
       </c>
       <c r="B6" t="n">
-        <v>100975</v>
+        <v>100976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,49 +1221,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129281694</v>
+        <v>129281691</v>
       </c>
       <c r="B7" t="n">
-        <v>100975</v>
+        <v>109631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222886</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516400</v>
+        <v>516350</v>
       </c>
       <c r="R7" t="n">
-        <v>6365033</v>
+        <v>6364947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129281691</v>
+        <v>129281692</v>
       </c>
       <c r="B8" t="n">
-        <v>109630</v>
+        <v>109419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516350</v>
+        <v>516380</v>
       </c>
       <c r="R8" t="n">
-        <v>6364947</v>
+        <v>6365010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,45 +1415,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129281692</v>
+        <v>129281694</v>
       </c>
       <c r="B9" t="n">
-        <v>109418</v>
+        <v>100976</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220228</v>
+        <v>222886</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Venen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516380</v>
+        <v>516400</v>
       </c>
       <c r="R9" t="n">
-        <v>6365010</v>
+        <v>6365033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
         <v>129281684</v>
       </c>
       <c r="B10" t="n">
-        <v>107478</v>
+        <v>107479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129281696</v>
       </c>
       <c r="B11" t="n">
-        <v>100975</v>
+        <v>100976</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129281683</v>
       </c>
       <c r="B12" t="n">
-        <v>109630</v>
+        <v>109631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>129281673</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>129281678</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>129281689</v>
       </c>
       <c r="B15" t="n">
-        <v>98805</v>
+        <v>98806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>129281670</v>
       </c>
       <c r="B16" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>129281680</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129281687</v>
       </c>
       <c r="B18" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129281679</v>
       </c>
       <c r="B19" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129281676</v>
+        <v>129281677</v>
       </c>
       <c r="B20" t="n">
-        <v>92907</v>
+        <v>92870</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516432</v>
+        <v>516446</v>
       </c>
       <c r="R20" t="n">
-        <v>6364723</v>
+        <v>6364783</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129281677</v>
+        <v>129281676</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>92908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516446</v>
+        <v>516432</v>
       </c>
       <c r="R21" t="n">
-        <v>6364783</v>
+        <v>6364723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>129281675</v>
       </c>
       <c r="B22" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>129281672</v>
       </c>
       <c r="B23" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>129281681</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
